--- a/uploads/M3M CALLING TW-3,2.xlsx
+++ b/uploads/M3M CALLING TW-3,2.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1028">
   <si>
     <t>Mr. ROMIT HOODA, DEWAK RAM HOODA</t>
   </si>
@@ -2929,6 +2929,201 @@
   </si>
   <si>
     <t>21000/- KA CLINT HO TO CALL KARNA </t>
+  </si>
+  <si>
+    <t>SELF USE</t>
+  </si>
+  <si>
+    <t>RENTED OUT</t>
+  </si>
+  <si>
+    <t>SALE KARNA HAI BUT ABHI NHI KRNA HAI </t>
+  </si>
+  <si>
+    <t>CALL</t>
+  </si>
+  <si>
+    <t>CALL MONDAY</t>
+  </si>
+  <si>
+    <t>CALLMONDAY</t>
+  </si>
+  <si>
+    <t>NETWORK NOT AVAILABEL</t>
+  </si>
+  <si>
+    <t>WRONG NUMBER </t>
+  </si>
+  <si>
+    <t>RENT SALE AVAILABEL 1.35L+MAINTENTION SALE PRICE 21000 KAMISAN 5L</t>
+  </si>
+  <si>
+    <t>AVAILABEL FOR RENT 85K INCULDING MAITANSITONS </t>
+  </si>
+  <si>
+    <t>CALL DECEMBER </t>
+  </si>
+  <si>
+    <t>I CALL YUO LETER</t>
+  </si>
+  <si>
+    <t>I CALL YOU LETER</t>
+  </si>
+  <si>
+    <t>AVAILABEL FOR SALE 19500-19200 TK NEGTIBEL KR LEGA A AUR B PART MIX HAI</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AVAILABEL FOR SALE </t>
+  </si>
+  <si>
+    <t>MH TW-02-701, 7F, M3M SKYCITY, Sector 65, Gu rugram, 122102,</t>
+  </si>
+  <si>
+    <t>AVAILABEL FOR SALE 19200</t>
+  </si>
+  <si>
+    <t>SWITCH OFF</t>
+  </si>
+  <si>
+    <t>SOLD OUT</t>
+  </si>
+  <si>
+    <t>SALE KRNA HAI BUT ABHI SOCHA NHII HAI</t>
+  </si>
+  <si>
+    <t>RENT 72-75 + MENTAINETION DO CAR PARKING</t>
+  </si>
+  <si>
+    <t>20000/-PAR SQ.FT. </t>
+  </si>
+  <si>
+    <t>MH TW-03-3101, 31F, M3M SKYCITY, Sector 65, Gurugram, 122102,</t>
+  </si>
+  <si>
+    <t>20000/- PER SQ.FT.</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>NOT VAILABEL</t>
+  </si>
+  <si>
+    <t>SWITCH OF</t>
+  </si>
+  <si>
+    <t>85K  INCULDING MAITAENTION</t>
+  </si>
+  <si>
+    <t>FOR SALE 2054,19500/-</t>
+  </si>
+  <si>
+    <t>2054, 80K INCULDING MAITAINESI</t>
+  </si>
+  <si>
+    <t>ABHI KUCHH NHI KRNA HAI JB HOGA TO CALL KAR LENGE </t>
+  </si>
+  <si>
+    <t>SELF USE </t>
+  </si>
+  <si>
+    <t>CALL NOT IPCK</t>
+  </si>
+  <si>
+    <t>INCOMING CALL NOT AVAILABEL</t>
+  </si>
+  <si>
+    <t>CALL LAGANA HAI FIR SE</t>
+  </si>
+  <si>
+    <t>KUNAL</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SALE OR RENT KA PUCHH KAR CALL RKH DIYA </t>
+  </si>
+  <si>
+    <t>2040/703</t>
+  </si>
+  <si>
+    <t>2040/703-18500</t>
+  </si>
+  <si>
+    <t>rented out</t>
+  </si>
+  <si>
+    <t>MH TW-03-2001, 20F, M3M SKYCITY, Sector 65, Gurugram, 122102,</t>
   </si>
 </sst>
 </file>
@@ -3311,7 +3506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BA6540-3663-4157-98C3-5F6829F2CC03}">
-  <dimension ref="A1:D359"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="59.28515625"/>
@@ -3327,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s" s="0">
         <v>950</v>
@@ -3623,6 +3818,9 @@
       <c r="C22" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="D22" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -3634,6 +3832,9 @@
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D23" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3645,6 +3846,9 @@
       <c r="C24" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="D24" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -3656,6 +3860,9 @@
       <c r="C25" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D25" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -3667,6 +3874,9 @@
       <c r="C26" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="D26" t="s" s="0">
+        <v>963</v>
+      </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -3678,6 +3888,9 @@
       <c r="C27" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="D27" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -3689,6 +3902,9 @@
       <c r="C28" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="D28" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -3700,6 +3916,9 @@
       <c r="C29" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="D29" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -3711,6 +3930,9 @@
       <c r="C30" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="D30" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -3722,6 +3944,9 @@
       <c r="C31" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="D31" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -3733,6 +3958,9 @@
       <c r="C32" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D32" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -3744,6 +3972,9 @@
       <c r="C33" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="D33" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -3755,6 +3986,9 @@
       <c r="C34" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="D34" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -3766,6 +4000,9 @@
       <c r="C35" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="D35" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -3777,6 +4014,9 @@
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D36" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -3788,6 +4028,9 @@
       <c r="C37" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D37" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -3799,6 +4042,9 @@
       <c r="C38" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="D38" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -3810,6 +4056,9 @@
       <c r="C39" s="1" t="s">
         <v>109</v>
       </c>
+      <c r="D39" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -3841,6 +4090,9 @@
       <c r="C42" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D42" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -3852,6 +4104,9 @@
       <c r="C43" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="D43" t="s" s="0">
+        <v>965</v>
+      </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
@@ -3863,6 +4118,9 @@
       <c r="C44" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="D44" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -3874,6 +4132,9 @@
       <c r="C45" s="1" t="s">
         <v>124</v>
       </c>
+      <c r="D45" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -3885,6 +4146,9 @@
       <c r="C46" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D46" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -3896,6 +4160,9 @@
       <c r="C47" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D47" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
@@ -3907,6 +4174,9 @@
       <c r="C48" s="1" t="s">
         <v>131</v>
       </c>
+      <c r="D48" t="s" s="0">
+        <v>967</v>
+      </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -3918,6 +4188,9 @@
       <c r="C49" s="1" t="s">
         <v>134</v>
       </c>
+      <c r="D49" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
@@ -3929,6 +4202,9 @@
       <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D50" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -3940,6 +4216,9 @@
       <c r="C51" s="1" t="s">
         <v>139</v>
       </c>
+      <c r="D51" t="s" s="0">
+        <v>967</v>
+      </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -3951,6 +4230,9 @@
       <c r="C52" s="1" t="s">
         <v>142</v>
       </c>
+      <c r="D52" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -3962,6 +4244,9 @@
       <c r="C53" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D53" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
@@ -3973,6 +4258,9 @@
       <c r="C54" s="1" t="s">
         <v>147</v>
       </c>
+      <c r="D54" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
@@ -3984,6 +4272,9 @@
       <c r="C55" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D55" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
@@ -3995,6 +4286,9 @@
       <c r="C56" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D56" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
@@ -4006,6 +4300,9 @@
       <c r="C57" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="D57" t="s" s="0">
+        <v>969</v>
+      </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
@@ -4017,6 +4314,9 @@
       <c r="C58" s="1" t="s">
         <v>157</v>
       </c>
+      <c r="D58" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
@@ -4028,6 +4328,9 @@
       <c r="C59" s="1" t="s">
         <v>160</v>
       </c>
+      <c r="D59" t="s" s="0">
+        <v>970</v>
+      </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -4039,6 +4342,9 @@
       <c r="C60" s="1" t="s">
         <v>163</v>
       </c>
+      <c r="D60" t="s" s="0">
+        <v>971</v>
+      </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
@@ -4050,6 +4356,9 @@
       <c r="C61" s="1" t="s">
         <v>166</v>
       </c>
+      <c r="D61" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -4061,6 +4370,9 @@
       <c r="C62" s="1" t="s">
         <v>169</v>
       </c>
+      <c r="D62" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
@@ -4072,6 +4384,9 @@
       <c r="C63" s="1" t="s">
         <v>169</v>
       </c>
+      <c r="D63" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
@@ -4083,6 +4398,9 @@
       <c r="C64" s="1" t="s">
         <v>174</v>
       </c>
+      <c r="D64" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
@@ -4094,6 +4412,9 @@
       <c r="C65" s="1" t="s">
         <v>174</v>
       </c>
+      <c r="D65" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
@@ -4105,6 +4426,9 @@
       <c r="C66" s="1" t="s">
         <v>179</v>
       </c>
+      <c r="D66" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
@@ -4116,6 +4440,9 @@
       <c r="C67" s="1" t="s">
         <v>182</v>
       </c>
+      <c r="D67" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
@@ -4127,6 +4454,9 @@
       <c r="C68" s="1" t="s">
         <v>185</v>
       </c>
+      <c r="D68" t="s" s="0">
+        <v>969</v>
+      </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
@@ -4138,6 +4468,9 @@
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D69" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
@@ -4149,6 +4482,9 @@
       <c r="C70" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D70" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
@@ -4180,6 +4516,9 @@
       <c r="C73" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="D73" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
@@ -4191,6 +4530,9 @@
       <c r="C74" s="1" t="s">
         <v>200</v>
       </c>
+      <c r="D74" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
@@ -4202,6 +4544,9 @@
       <c r="C75" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="D75" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
@@ -4213,6 +4558,9 @@
       <c r="C76" s="1" t="s">
         <v>206</v>
       </c>
+      <c r="D76" t="s" s="0">
+        <v>959</v>
+      </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
@@ -4224,6 +4572,9 @@
       <c r="C77" s="1" t="s">
         <v>209</v>
       </c>
+      <c r="D77" t="s" s="0">
+        <v>981</v>
+      </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
@@ -4235,6 +4586,9 @@
       <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D78" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
@@ -4246,6 +4600,9 @@
       <c r="C79" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="D79" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
@@ -4257,6 +4614,9 @@
       <c r="C80" s="1" t="s">
         <v>217</v>
       </c>
+      <c r="D80" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
@@ -4268,6 +4628,9 @@
       <c r="C81" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D81" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
@@ -4288,6 +4651,9 @@
       <c r="C83" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="D83" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
@@ -4299,6 +4665,9 @@
       <c r="C84" s="1" t="s">
         <v>227</v>
       </c>
+      <c r="D84" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
@@ -4310,6 +4679,9 @@
       <c r="C85" s="1" t="s">
         <v>230</v>
       </c>
+      <c r="D85" t="s" s="0">
+        <v>982</v>
+      </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
@@ -4321,6 +4693,9 @@
       <c r="C86" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D86" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
@@ -4332,6 +4707,9 @@
       <c r="C87" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D87" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
@@ -4343,6 +4721,9 @@
       <c r="C88" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="D88" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
@@ -4354,6 +4735,9 @@
       <c r="C89" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="D89" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
@@ -4365,6 +4749,9 @@
       <c r="C90" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D90" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -4376,6 +4763,9 @@
       <c r="C91" s="1" t="s">
         <v>245</v>
       </c>
+      <c r="D91" t="s" s="0">
+        <v>981</v>
+      </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
@@ -4387,6 +4777,9 @@
       <c r="C92" s="1" t="s">
         <v>248</v>
       </c>
+      <c r="D92" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
@@ -4398,6 +4791,9 @@
       <c r="C93" s="1" t="s">
         <v>251</v>
       </c>
+      <c r="D93" t="s" s="0">
+        <v>959</v>
+      </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
@@ -4409,6 +4805,9 @@
       <c r="C94" s="1" t="s">
         <v>254</v>
       </c>
+      <c r="D94" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
@@ -4420,6 +4819,9 @@
       <c r="C95" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="D95" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
@@ -4431,6 +4833,9 @@
       <c r="C96" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="D96" t="s" s="0">
+        <v>969</v>
+      </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
@@ -4442,6 +4847,9 @@
       <c r="C97" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="D97" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
@@ -4453,6 +4861,9 @@
       <c r="C98" s="1" t="s">
         <v>266</v>
       </c>
+      <c r="D98" t="s" s="0">
+        <v>963</v>
+      </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
@@ -4464,6 +4875,9 @@
       <c r="C99" s="1" t="s">
         <v>269</v>
       </c>
+      <c r="D99" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
@@ -4475,6 +4889,9 @@
       <c r="C100" s="1" t="s">
         <v>272</v>
       </c>
+      <c r="D100" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
@@ -4486,6 +4903,9 @@
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D101" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
@@ -4497,6 +4917,9 @@
       <c r="C102" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="D102" t="s" s="0">
+        <v>983</v>
+      </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
@@ -4508,6 +4931,9 @@
       <c r="C103" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="D103" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
@@ -4519,6 +4945,9 @@
       <c r="C104" s="1" t="s">
         <v>283</v>
       </c>
+      <c r="D104" t="s" s="0">
+        <v>955</v>
+      </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
@@ -4530,6 +4959,9 @@
       <c r="C105" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D105" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
@@ -4541,16 +4973,22 @@
       <c r="C106" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D106" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>288</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>289</v>
+        <v>1027</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>290</v>
+      </c>
+      <c r="D107" t="s" s="0">
+        <v>984</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4563,6 +5001,9 @@
       <c r="C108" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D108" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
@@ -4574,6 +5015,9 @@
       <c r="C109" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D109" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
@@ -4585,6 +5029,9 @@
       <c r="C110" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D110" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
@@ -4596,6 +5043,9 @@
       <c r="C111" s="1" t="s">
         <v>299</v>
       </c>
+      <c r="D111" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
@@ -4607,6 +5057,9 @@
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D112" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
@@ -4618,6 +5071,9 @@
       <c r="C113" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="D113" t="s" s="0">
+        <v>985</v>
+      </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
@@ -4629,6 +5085,9 @@
       <c r="C114" s="1" t="s">
         <v>307</v>
       </c>
+      <c r="D114" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
@@ -4640,6 +5099,9 @@
       <c r="C115" s="1" t="s">
         <v>310</v>
       </c>
+      <c r="D115" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -4651,6 +5113,9 @@
       <c r="C116" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D116" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
@@ -4662,6 +5127,9 @@
       <c r="C117" s="1" t="s">
         <v>315</v>
       </c>
+      <c r="D117" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
@@ -4673,6 +5141,9 @@
       <c r="C118" s="1" t="s">
         <v>318</v>
       </c>
+      <c r="D118" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
@@ -4684,6 +5155,9 @@
       <c r="C119" s="1" t="s">
         <v>321</v>
       </c>
+      <c r="D119" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
@@ -4695,6 +5169,9 @@
       <c r="C120" s="1" t="s">
         <v>324</v>
       </c>
+      <c r="D120" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
@@ -4706,6 +5183,9 @@
       <c r="C121" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D121" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
@@ -4717,6 +5197,9 @@
       <c r="C122" s="1" t="s">
         <v>329</v>
       </c>
+      <c r="D122" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
@@ -4728,6 +5211,9 @@
       <c r="C123" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D123" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
@@ -4739,6 +5225,9 @@
       <c r="C124" s="1" t="s">
         <v>334</v>
       </c>
+      <c r="D124" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
@@ -4750,6 +5239,9 @@
       <c r="C125" s="1" t="s">
         <v>337</v>
       </c>
+      <c r="D125" t="s" s="0">
+        <v>955</v>
+      </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
@@ -4761,6 +5253,9 @@
       <c r="C126" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D126" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
@@ -4772,16 +5267,22 @@
       <c r="C127" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D127" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>342</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>343</v>
+        <v>986</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>344</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>987</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4794,6 +5295,9 @@
       <c r="C129" s="1" t="s">
         <v>347</v>
       </c>
+      <c r="D129" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
@@ -4805,6 +5309,9 @@
       <c r="C130" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="D130" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
@@ -4816,6 +5323,9 @@
       <c r="C131" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="D131" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
@@ -4827,6 +5337,9 @@
       <c r="C132" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D132" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
@@ -4838,6 +5351,9 @@
       <c r="C133" s="1" t="s">
         <v>357</v>
       </c>
+      <c r="D133" t="s" s="0">
+        <v>963</v>
+      </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
@@ -4849,6 +5365,9 @@
       <c r="C134" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D134" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -4860,6 +5379,9 @@
       <c r="C135" s="1" t="s">
         <v>362</v>
       </c>
+      <c r="D135" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
@@ -4871,6 +5393,9 @@
       <c r="C136" s="1" t="s">
         <v>365</v>
       </c>
+      <c r="D136" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
@@ -4882,6 +5407,9 @@
       <c r="C137" s="1" t="s">
         <v>365</v>
       </c>
+      <c r="D137" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
@@ -4893,6 +5421,9 @@
       <c r="C138" s="1" t="s">
         <v>370</v>
       </c>
+      <c r="D138" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
@@ -4904,6 +5435,9 @@
       <c r="C139" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D139" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
@@ -4915,6 +5449,9 @@
       <c r="C140" s="1" t="s">
         <v>375</v>
       </c>
+      <c r="D140" t="s" s="0">
+        <v>981</v>
+      </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
@@ -4926,6 +5463,9 @@
       <c r="C141" s="1" t="s">
         <v>378</v>
       </c>
+      <c r="D141" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
@@ -4937,6 +5477,9 @@
       <c r="C142" s="1" t="s">
         <v>381</v>
       </c>
+      <c r="D142" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
@@ -4948,6 +5491,9 @@
       <c r="C143" s="1" t="s">
         <v>384</v>
       </c>
+      <c r="D143" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
@@ -4959,6 +5505,9 @@
       <c r="C144" s="1" t="s">
         <v>387</v>
       </c>
+      <c r="D144" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
@@ -4970,6 +5519,9 @@
       <c r="C145" s="1" t="s">
         <v>390</v>
       </c>
+      <c r="D145" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
@@ -4981,6 +5533,9 @@
       <c r="C146" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D146" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
@@ -4992,6 +5547,9 @@
       <c r="C147" s="1" t="s">
         <v>395</v>
       </c>
+      <c r="D147" t="s" s="0">
+        <v>959</v>
+      </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
@@ -5003,6 +5561,9 @@
       <c r="C148" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D148" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
@@ -5014,6 +5575,9 @@
       <c r="C149" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D149" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
@@ -5025,6 +5589,9 @@
       <c r="C150" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="D150" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
@@ -5036,6 +5603,9 @@
       <c r="C151" s="1" t="s">
         <v>405</v>
       </c>
+      <c r="D151" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
@@ -5047,6 +5617,9 @@
       <c r="C152" s="1" t="s">
         <v>408</v>
       </c>
+      <c r="D152" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
@@ -5058,6 +5631,9 @@
       <c r="C153" s="1" t="s">
         <v>411</v>
       </c>
+      <c r="D153" t="s" s="0">
+        <v>998</v>
+      </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
@@ -5069,6 +5645,9 @@
       <c r="C154" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="D154" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
@@ -5080,6 +5659,9 @@
       <c r="C155" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="D155" t="s" s="0">
+        <v>995</v>
+      </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
@@ -5091,6 +5673,9 @@
       <c r="C156" s="1" t="s">
         <v>419</v>
       </c>
+      <c r="D156" t="s" s="0">
+        <v>996</v>
+      </c>
     </row>
     <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
@@ -5102,6 +5687,9 @@
       <c r="C157" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D157" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
@@ -5113,6 +5701,9 @@
       <c r="C158" s="1" t="s">
         <v>424</v>
       </c>
+      <c r="D158" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
@@ -5124,6 +5715,9 @@
       <c r="C159" s="1" t="s">
         <v>427</v>
       </c>
+      <c r="D159" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
@@ -5135,6 +5729,9 @@
       <c r="C160" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D160" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
@@ -5146,6 +5743,9 @@
       <c r="C161" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D161" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
@@ -5157,6 +5757,9 @@
       <c r="C162" s="1" t="s">
         <v>433</v>
       </c>
+      <c r="D162" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
@@ -5168,6 +5771,9 @@
       <c r="C163" s="1" t="s">
         <v>436</v>
       </c>
+      <c r="D163" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
@@ -5179,6 +5785,9 @@
       <c r="C164" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D164" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
@@ -5190,6 +5799,9 @@
       <c r="C165" s="1" t="s">
         <v>441</v>
       </c>
+      <c r="D165" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
@@ -5201,6 +5813,9 @@
       <c r="C166" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D166" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
@@ -5212,6 +5827,9 @@
       <c r="C167" s="1" t="s">
         <v>446</v>
       </c>
+      <c r="D167" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
@@ -5223,6 +5841,9 @@
       <c r="C168" s="1" t="s">
         <v>449</v>
       </c>
+      <c r="D168" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
@@ -5234,6 +5855,9 @@
       <c r="C169" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D169" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
@@ -5245,6 +5869,9 @@
       <c r="C170" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D170" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
@@ -5256,6 +5883,9 @@
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D171" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
@@ -5267,6 +5897,9 @@
       <c r="C172" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D172" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
@@ -5278,6 +5911,9 @@
       <c r="C173" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D173" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
@@ -5289,6 +5925,9 @@
       <c r="C174" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D174" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
@@ -5300,6 +5939,9 @@
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D175" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
@@ -5311,6 +5953,9 @@
       <c r="C176" s="1" t="s">
         <v>466</v>
       </c>
+      <c r="D176" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
@@ -5322,6 +5967,9 @@
       <c r="C177" s="1" t="s">
         <v>469</v>
       </c>
+      <c r="D177" t="s" s="0">
+        <v>997</v>
+      </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
@@ -5333,6 +5981,9 @@
       <c r="C178" s="1" t="s">
         <v>472</v>
       </c>
+      <c r="D178" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
@@ -5344,6 +5995,9 @@
       <c r="C179" s="1" t="s">
         <v>475</v>
       </c>
+      <c r="D179" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
@@ -5355,6 +6009,9 @@
       <c r="C180" s="1" t="s">
         <v>478</v>
       </c>
+      <c r="D180" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
@@ -5366,6 +6023,9 @@
       <c r="C181" s="1" t="s">
         <v>481</v>
       </c>
+      <c r="D181" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
@@ -5377,6 +6037,9 @@
       <c r="C182" s="1" t="s">
         <v>478</v>
       </c>
+      <c r="D182" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
@@ -5388,6 +6051,9 @@
       <c r="C183" s="1" t="s">
         <v>485</v>
       </c>
+      <c r="D183" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
@@ -5399,6 +6065,9 @@
       <c r="C184" s="1" t="s">
         <v>488</v>
       </c>
+      <c r="D184" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
@@ -5410,6 +6079,9 @@
       <c r="C185" s="1" t="s">
         <v>488</v>
       </c>
+      <c r="D185" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
@@ -5421,6 +6093,9 @@
       <c r="C186" s="1" t="s">
         <v>492</v>
       </c>
+      <c r="D186" t="s" s="0">
+        <v>972</v>
+      </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
@@ -5432,6 +6107,9 @@
       <c r="C187" s="1" t="s">
         <v>495</v>
       </c>
+      <c r="D187" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
@@ -5443,6 +6121,9 @@
       <c r="C188" s="1" t="s">
         <v>498</v>
       </c>
+      <c r="D188" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
@@ -5454,6 +6135,9 @@
       <c r="C189" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="D189" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
@@ -5465,6 +6149,9 @@
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D190" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
@@ -5476,6 +6163,9 @@
       <c r="C191" s="1" t="s">
         <v>505</v>
       </c>
+      <c r="D191" t="s" s="0">
+        <v>973</v>
+      </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
@@ -5487,6 +6177,9 @@
       <c r="C192" s="1" t="s">
         <v>508</v>
       </c>
+      <c r="D192" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
@@ -5498,6 +6191,9 @@
       <c r="C193" s="1" t="s">
         <v>511</v>
       </c>
+      <c r="D193" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
@@ -5509,6 +6205,9 @@
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D194" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
@@ -5520,6 +6219,9 @@
       <c r="C195" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D195" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
@@ -5531,6 +6233,9 @@
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D196" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
@@ -5542,6 +6247,9 @@
       <c r="C197" s="1" t="s">
         <v>520</v>
       </c>
+      <c r="D197" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
@@ -5553,6 +6261,9 @@
       <c r="C198" s="1" t="s">
         <v>523</v>
       </c>
+      <c r="D198" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
@@ -5564,6 +6275,9 @@
       <c r="C199" s="1" t="s">
         <v>526</v>
       </c>
+      <c r="D199" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
@@ -5575,6 +6289,9 @@
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D200" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
@@ -5586,6 +6303,9 @@
       <c r="C201" s="1" t="s">
         <v>531</v>
       </c>
+      <c r="D201" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
@@ -5597,6 +6317,9 @@
       <c r="C202" s="1" t="s">
         <v>534</v>
       </c>
+      <c r="D202" t="s" s="0">
+        <v>963</v>
+      </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
@@ -5608,6 +6331,9 @@
       <c r="C203" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D203" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
@@ -5619,6 +6345,9 @@
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D204" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
@@ -5630,6 +6359,9 @@
       <c r="C205" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D205" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
@@ -5641,6 +6373,9 @@
       <c r="C206" s="1" t="s">
         <v>543</v>
       </c>
+      <c r="D206" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
@@ -5674,6 +6409,9 @@
       <c r="C209" s="1" t="s">
         <v>550</v>
       </c>
+      <c r="D209" t="s" s="0">
+        <v>989</v>
+      </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
@@ -5685,6 +6423,9 @@
       <c r="C210" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D210" t="s" s="0">
+        <v>954</v>
+      </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
@@ -5696,6 +6437,9 @@
       <c r="C211" s="1" t="s">
         <v>555</v>
       </c>
+      <c r="D211" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
@@ -5707,6 +6451,9 @@
       <c r="C212" s="1" t="s">
         <v>558</v>
       </c>
+      <c r="D212" t="s" s="0">
+        <v>990</v>
+      </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
@@ -5718,6 +6465,9 @@
       <c r="C213" s="1" t="s">
         <v>561</v>
       </c>
+      <c r="D213" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
@@ -5729,6 +6479,9 @@
       <c r="C214" s="1" t="s">
         <v>564</v>
       </c>
+      <c r="D214" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
@@ -5740,6 +6493,9 @@
       <c r="C215" s="1" t="s">
         <v>567</v>
       </c>
+      <c r="D215" t="s" s="0">
+        <v>959</v>
+      </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
@@ -5751,6 +6507,9 @@
       <c r="C216" s="1" t="s">
         <v>570</v>
       </c>
+      <c r="D216" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
@@ -5762,6 +6521,9 @@
       <c r="C217" s="1" t="s">
         <v>573</v>
       </c>
+      <c r="D217" t="s" s="0">
+        <v>981</v>
+      </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
@@ -5773,6 +6535,9 @@
       <c r="C218" s="1" t="s">
         <v>576</v>
       </c>
+      <c r="D218" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
@@ -5784,6 +6549,9 @@
       <c r="C219" s="1" t="s">
         <v>579</v>
       </c>
+      <c r="D219" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
@@ -5795,6 +6563,9 @@
       <c r="C220" s="1" t="s">
         <v>582</v>
       </c>
+      <c r="D220" t="s" s="0">
+        <v>1026</v>
+      </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
@@ -5806,6 +6577,9 @@
       <c r="C221" s="1" t="s">
         <v>585</v>
       </c>
+      <c r="D221" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
@@ -5817,6 +6591,9 @@
       <c r="C222" s="1" t="s">
         <v>588</v>
       </c>
+      <c r="D222" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -5828,6 +6605,9 @@
       <c r="C223" s="1" t="s">
         <v>591</v>
       </c>
+      <c r="D223" t="s" s="0">
+        <v>953</v>
+      </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
@@ -5839,6 +6619,9 @@
       <c r="C224" s="1" t="s">
         <v>594</v>
       </c>
+      <c r="D224" t="s" s="0">
+        <v>1023</v>
+      </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
@@ -5850,6 +6633,9 @@
       <c r="C225" s="1" t="s">
         <v>597</v>
       </c>
+      <c r="D225" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
@@ -5861,6 +6647,9 @@
       <c r="C226" s="1" t="s">
         <v>600</v>
       </c>
+      <c r="D226" t="s" s="0">
+        <v>992</v>
+      </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
@@ -5872,6 +6661,9 @@
       <c r="C227" s="1" t="s">
         <v>603</v>
       </c>
+      <c r="D227" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
@@ -5883,6 +6675,9 @@
       <c r="C228" s="1" t="s">
         <v>606</v>
       </c>
+      <c r="D228" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
@@ -5905,6 +6700,9 @@
       <c r="C230" s="1" t="s">
         <v>611</v>
       </c>
+      <c r="D230" t="s" s="0">
+        <v>963</v>
+      </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
@@ -5916,6 +6714,9 @@
       <c r="C231" s="1" t="s">
         <v>614</v>
       </c>
+      <c r="D231" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
@@ -5927,6 +6728,9 @@
       <c r="C232" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D232" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
@@ -5938,6 +6742,9 @@
       <c r="C233" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D233" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
@@ -5949,6 +6756,9 @@
       <c r="C234" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D234" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
@@ -5982,6 +6792,9 @@
       <c r="C237" s="1" t="s">
         <v>629</v>
       </c>
+      <c r="D237" t="s" s="0">
+        <v>955</v>
+      </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
@@ -6026,6 +6839,9 @@
       <c r="C241" s="1" t="s">
         <v>639</v>
       </c>
+      <c r="D241" t="s" s="0">
+        <v>981</v>
+      </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
@@ -6070,6 +6886,9 @@
       <c r="C245" s="1" t="s">
         <v>649</v>
       </c>
+      <c r="D245" t="s" s="0">
+        <v>993</v>
+      </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
@@ -6110,6 +6929,9 @@
       <c r="C249" s="1" t="s">
         <v>659</v>
       </c>
+      <c r="D249" t="s" s="0">
+        <v>959</v>
+      </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
@@ -6286,6 +7108,9 @@
       <c r="C265" s="1" t="s">
         <v>704</v>
       </c>
+      <c r="D265" t="s" s="0">
+        <v>954</v>
+      </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
@@ -6297,6 +7122,9 @@
       <c r="C266" s="1" t="s">
         <v>707</v>
       </c>
+      <c r="D266" t="s" s="0">
+        <v>1025</v>
+      </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
@@ -6933,6 +7761,9 @@
       <c r="C324" s="1" t="s">
         <v>858</v>
       </c>
+      <c r="D324" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
@@ -7153,6 +7984,9 @@
       <c r="C344" s="1" t="s">
         <v>910</v>
       </c>
+      <c r="D344" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
@@ -7236,10 +8070,13 @@
         <v>928</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>929</v>
+        <v>979</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>930</v>
+      </c>
+      <c r="D352" t="s" s="0">
+        <v>958</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7252,6 +8089,9 @@
       <c r="C353" s="1" t="s">
         <v>933</v>
       </c>
+      <c r="D353" t="s" s="0">
+        <v>975</v>
+      </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
@@ -7296,6 +8136,9 @@
       <c r="C357" s="1" t="s">
         <v>943</v>
       </c>
+      <c r="D357" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
@@ -7317,6 +8160,90 @@
       </c>
       <c r="C359" s="1" t="s">
         <v>949</v>
+      </c>
+      <c r="D359" t="s" s="0">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="0">
+        <v>1000</v>
+      </c>
+      <c r="B360" t="s" s="0">
+        <v>1001</v>
+      </c>
+      <c r="C360" t="s" s="0">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="0">
+        <v>1003</v>
+      </c>
+      <c r="B361" t="s" s="0">
+        <v>1004</v>
+      </c>
+      <c r="C361" t="s" s="0">
+        <v>1005</v>
+      </c>
+      <c r="D361" t="s" s="0">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="0">
+        <v>1007</v>
+      </c>
+      <c r="B362" t="s" s="0">
+        <v>1008</v>
+      </c>
+      <c r="C362" t="s" s="0">
+        <v>1009</v>
+      </c>
+      <c r="D362" t="s" s="0">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="0">
+        <v>1011</v>
+      </c>
+      <c r="B363" t="s" s="0">
+        <v>1012</v>
+      </c>
+      <c r="C363" t="s" s="0">
+        <v>1013</v>
+      </c>
+      <c r="D363" t="s" s="0">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="0">
+        <v>1015</v>
+      </c>
+      <c r="B364" t="s" s="0">
+        <v>1016</v>
+      </c>
+      <c r="C364" t="s" s="0">
+        <v>1017</v>
+      </c>
+      <c r="D364" t="s" s="0">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="0">
+        <v>1019</v>
+      </c>
+      <c r="B365" t="s" s="0">
+        <v>1020</v>
+      </c>
+      <c r="C365" t="s" s="0">
+        <v>1021</v>
+      </c>
+      <c r="D365" t="s" s="0">
+        <v>1022</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/M3M CALLING TW-3,2.xlsx
+++ b/uploads/M3M CALLING TW-3,2.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="1031">
   <si>
     <t>Mr. ROMIT HOODA, DEWAK RAM HOODA</t>
   </si>
@@ -3124,6 +3124,15 @@
   </si>
   <si>
     <t>MH TW-03-2001, 20F, M3M SKYCITY, Sector 65, Gurugram, 122102,</t>
+  </si>
+  <si>
+    <t>APNE BETE SE BAAT KAR KE BTAYE GI</t>
+  </si>
+  <si>
+    <t>19200 FULL</t>
+  </si>
+  <si>
+    <t>85K+MAINT+ELECTRIC+CLUB</t>
   </si>
 </sst>
 </file>
@@ -6387,6 +6396,9 @@
       <c r="C207" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="D207" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
@@ -6398,6 +6410,9 @@
       <c r="C208" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D208" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
@@ -6770,6 +6785,9 @@
       <c r="C235" s="1" t="s">
         <v>623</v>
       </c>
+      <c r="D235" t="s" s="0">
+        <v>1028</v>
+      </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
@@ -6806,6 +6824,9 @@
       <c r="C238" s="1" t="s">
         <v>511</v>
       </c>
+      <c r="D238" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
@@ -6817,6 +6838,9 @@
       <c r="C239" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D239" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
@@ -6828,6 +6852,9 @@
       <c r="C240" s="1" t="s">
         <v>636</v>
       </c>
+      <c r="D240" t="s" s="0">
+        <v>1029</v>
+      </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
@@ -6853,6 +6880,9 @@
       <c r="C242" s="1" t="s">
         <v>642</v>
       </c>
+      <c r="D242" t="s" s="0">
+        <v>964</v>
+      </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
@@ -6864,6 +6894,9 @@
       <c r="C243" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D243" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
@@ -6875,6 +6908,9 @@
       <c r="C244" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D244" t="s" s="0">
+        <v>952</v>
+      </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
@@ -6900,6 +6936,9 @@
       <c r="C246" s="1" t="s">
         <v>652</v>
       </c>
+      <c r="D246" t="s" s="0">
+        <v>1030</v>
+      </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
@@ -6943,6 +6982,9 @@
       <c r="C250" s="1" t="s">
         <v>662</v>
       </c>
+      <c r="D250" t="s" s="0">
+        <v>950</v>
+      </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
@@ -7433,6 +7475,9 @@
       <c r="C294" s="1" t="s">
         <v>781</v>
       </c>
+      <c r="D294" t="s" s="0">
+        <v>960</v>
+      </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
@@ -7444,6 +7489,9 @@
       <c r="C295" s="1" t="s">
         <v>784</v>
       </c>
+      <c r="D295" t="s" s="0">
+        <v>958</v>
+      </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
@@ -7454,6 +7502,9 @@
       </c>
       <c r="C296" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="D296" t="s" s="0">
+        <v>956</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
